--- a/Spine_Projects/01_input_data/01_input_raw/Products/diesel/Model_Data_Base_diesel.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/diesel/Model_Data_Base_diesel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/djh_eco_cbs_dk/Documents/Documents/GitHub/Nord_H2ub/Spine_Projects/01_input_data/01_input_raw/Products/diesel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\diesel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{B5F29A4A-EA87-4677-8B97-7434E8C6C701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70518CDC-0953-4002-8148-6128F0931880}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD77EA04-898D-4C4A-8105-DC02AD318C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="137">
   <si>
     <t>Unit</t>
   </si>
@@ -458,6 +458,33 @@
   </si>
   <si>
     <t>60h</t>
+  </si>
+  <si>
+    <t>solar_plant_node</t>
+  </si>
+  <si>
+    <t>wind_onshore_plant_node</t>
+  </si>
+  <si>
+    <t>wind_offshore_plant_node</t>
+  </si>
+  <si>
+    <t>pl_wholesale_solar</t>
+  </si>
+  <si>
+    <t>pl_solar_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_onshore</t>
+  </si>
+  <si>
+    <t>pl_wind_onshore_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_offshore</t>
+  </si>
+  <si>
+    <t>pl_wind_offshore_PPA</t>
   </si>
 </sst>
 </file>
@@ -548,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -561,14 +588,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -579,6 +605,9 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1340,8 +1369,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA5" totalsRowShown="0">
-  <autoFilter ref="A1:AA5" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA11" totalsRowShown="0">
+  <autoFilter ref="A1:AA11" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{26B0CA71-1EA9-44CF-8E6D-31054ECA99A6}" name="Connection"/>
     <tableColumn id="26" xr3:uid="{E67F4435-EF76-417C-B715-53719E5FB41F}" name="Object_type"/>
@@ -1349,7 +1378,7 @@
     <tableColumn id="3" xr3:uid="{0B221EED-10BC-4C34-AC5E-37A826B1E8AE}" name="Input2"/>
     <tableColumn id="4" xr3:uid="{13095F0A-BCF6-40A3-B029-60B11214B154}" name="Output1"/>
     <tableColumn id="5" xr3:uid="{4C6B3E52-C4A2-4D67-B50B-9DAA089E0399}" name="Output2"/>
-    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Connection_type" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Connection_type" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{5DF4D35D-AD4C-4648-BC90-B2BA8F975A09}" name="Cap_Input1_existing"/>
     <tableColumn id="15" xr3:uid="{C0BCA9EF-0E20-40E5-9820-0EA6AB1DE457}" name="Cap_Input1_max"/>
     <tableColumn id="14" xr3:uid="{D4F16D16-99DE-47DA-B08A-6DD56FEBC7A4}" name="Cap_Input2_existing"/>
@@ -1368,7 +1397,7 @@
     <tableColumn id="21" xr3:uid="{EC2CC790-C17D-4744-A981-3984808E5B33}" name="vom_cost_Input2"/>
     <tableColumn id="24" xr3:uid="{41B338E4-2058-41E9-8000-97D77450FBC3}" name="vom_cost_Output1"/>
     <tableColumn id="25" xr3:uid="{DDAFCF0A-1EF1-4B7B-9742-01F9FA7A22E5}" name="vom_cost_Output2"/>
-    <tableColumn id="29" xr3:uid="{79DE3A19-CED6-47DE-AEF5-F6BB2D320F24}" name="connection_investment_tech_lifetime" dataDxfId="1"/>
+    <tableColumn id="29" xr3:uid="{79DE3A19-CED6-47DE-AEF5-F6BB2D320F24}" name="connection_investment_tech_lifetime" dataDxfId="0"/>
     <tableColumn id="30" xr3:uid="{09434E4A-7BF5-4547-9708-EA3F0F7ADC8E}" name="initial_connections_invested_available"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1379,7 +1408,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}" name="Table134" displayName="Table134" ref="A1:K5" totalsRowShown="0">
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="2">
       <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A100,ISNUMBER(FIND("storage",Connections!A2:A100)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{8C29206C-8DC6-44DB-A8D1-3D5625C277AD}" name="Object_type"/>
@@ -1705,22 +1734,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" customWidth="1"/>
-    <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="10.54296875" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1776,7 +1805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1784,12 +1813,12 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1797,12 +1826,12 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -1810,12 +1839,12 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -1837,7 +1866,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -1850,7 +1879,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -1867,7 +1896,7 @@
         <v>20.192799999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -1880,7 +1909,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -1896,7 +1925,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -1909,7 +1938,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -1922,7 +1951,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>117</v>
       </c>
@@ -1944,7 +1973,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>124</v>
       </c>
@@ -1957,7 +1986,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>125</v>
       </c>
@@ -2000,14 +2029,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="13.26953125" customWidth="1"/>
-    <col min="7" max="8" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="7" max="8" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2060,7 +2089,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>69</v>
       </c>
@@ -2071,8 +2100,8 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
-        <v>70</v>
+      <c r="G2" t="s">
+        <v>128</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="7"/>
@@ -2085,7 +2114,7 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>102</v>
       </c>
@@ -2096,8 +2125,8 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>70</v>
+      <c r="G3" t="s">
+        <v>129</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -2110,7 +2139,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -2121,8 +2150,8 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>70</v>
+      <c r="G4" t="s">
+        <v>130</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -2135,7 +2164,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>85</v>
       </c>
@@ -2170,7 +2199,7 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>81</v>
       </c>
@@ -2203,7 +2232,7 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -2240,7 +2269,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -2281,7 +2310,7 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -2314,7 +2343,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -2331,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -2360,7 +2389,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>117</v>
       </c>
@@ -2407,7 +2436,7 @@
       </c>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>124</v>
       </c>
@@ -2436,7 +2465,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>125</v>
       </c>
@@ -2488,34 +2517,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AA11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.26953125" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" customWidth="1"/>
-    <col min="10" max="10" width="15.453125" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="10.54296875" customWidth="1"/>
-    <col min="17" max="17" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.81640625" customWidth="1"/>
-    <col min="21" max="21" width="12.81640625" customWidth="1"/>
-    <col min="22" max="23" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="35.26953125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.85546875" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" customWidth="1"/>
+    <col min="22" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -2598,7 +2627,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -2657,7 +2686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -2713,7 +2742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>121</v>
       </c>
@@ -2739,7 +2768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -2774,6 +2803,297 @@
         <v>58</v>
       </c>
       <c r="AA5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
+        <v>1000</v>
+      </c>
+      <c r="M6">
+        <v>1000</v>
+      </c>
+      <c r="N6">
+        <v>1000</v>
+      </c>
+      <c r="O6">
+        <v>1000</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>1000</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1000</v>
+      </c>
+      <c r="M7">
+        <v>1000</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>1000</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1000</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>1000</v>
+      </c>
+      <c r="M8">
+        <v>1000</v>
+      </c>
+      <c r="N8">
+        <v>1000</v>
+      </c>
+      <c r="O8">
+        <v>1000</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>1000</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>1000</v>
+      </c>
+      <c r="M9">
+        <v>1000</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10">
+        <v>1000</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="J10">
+        <v>1000</v>
+      </c>
+      <c r="K10">
+        <v>1000</v>
+      </c>
+      <c r="L10">
+        <v>1000</v>
+      </c>
+      <c r="M10">
+        <v>1000</v>
+      </c>
+      <c r="N10">
+        <v>1000</v>
+      </c>
+      <c r="O10">
+        <v>1000</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11">
+        <v>1000</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="L11">
+        <v>1000</v>
+      </c>
+      <c r="M11">
+        <v>1000</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA11">
         <v>1</v>
       </c>
     </row>
@@ -2802,22 +3122,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1796875" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -2852,7 +3172,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -2878,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>122</v>
       </c>
@@ -2933,127 +3253,127 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DC79B9-9C58-497E-9FD8-D3F2239E9BDC}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>126</v>
       </c>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/diesel/Model_Data_Base_diesel.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/diesel/Model_Data_Base_diesel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\diesel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD77EA04-898D-4C4A-8105-DC02AD318C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FFF786-3F88-4F30-AF42-3C5AA8EDFD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="136">
   <si>
     <t>Unit</t>
   </si>
@@ -337,12 +337,6 @@
     <t>initial_units_on</t>
   </si>
   <si>
-    <t>heat_low</t>
-  </si>
-  <si>
-    <t>heat_high</t>
-  </si>
-  <si>
     <t>Auxilliary</t>
   </si>
   <si>
@@ -448,9 +442,6 @@
     <t>co2_source</t>
   </si>
   <si>
-    <t>heat_recovery</t>
-  </si>
-  <si>
     <t>power_steam</t>
   </si>
   <si>
@@ -485,13 +476,19 @@
   </si>
   <si>
     <t>pl_wind_offshore_PPA</t>
+  </si>
+  <si>
+    <t>excess_heat</t>
+  </si>
+  <si>
+    <t>heat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,6 +506,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -575,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -588,13 +592,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -605,9 +611,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1316,8 +1319,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}" name="Table1" displayName="Table1" ref="A1:R14" totalsRowShown="0">
-  <autoFilter ref="A1:R14" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}" name="Table1" displayName="Table1" ref="A1:R13" totalsRowShown="0">
+  <autoFilter ref="A1:R13" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{C73E51D0-1842-42F3-9C00-F0DBD2E661BE}" name="Unit"/>
     <tableColumn id="40" xr3:uid="{C2CFC5A4-5329-4F74-926A-18CEB18C062C}" name="Object_type"/>
@@ -1343,8 +1346,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}" name="Table5" displayName="Table5" ref="A1:Q14" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:Q14" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}" name="Table5" displayName="Table5" ref="A1:Q13" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:Q13" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{2BE3E317-773B-4E82-9035-69A43C6CB21B}" name="Unit" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{22613EE0-390D-4B04-9A9B-6D5554D1C8ED}" name="Object_type" dataDxfId="18"/>
@@ -1378,7 +1381,7 @@
     <tableColumn id="3" xr3:uid="{0B221EED-10BC-4C34-AC5E-37A826B1E8AE}" name="Input2"/>
     <tableColumn id="4" xr3:uid="{13095F0A-BCF6-40A3-B029-60B11214B154}" name="Output1"/>
     <tableColumn id="5" xr3:uid="{4C6B3E52-C4A2-4D67-B50B-9DAA089E0399}" name="Output2"/>
-    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Connection_type" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Connection_type" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{5DF4D35D-AD4C-4648-BC90-B2BA8F975A09}" name="Cap_Input1_existing"/>
     <tableColumn id="15" xr3:uid="{C0BCA9EF-0E20-40E5-9820-0EA6AB1DE457}" name="Cap_Input1_max"/>
     <tableColumn id="14" xr3:uid="{D4F16D16-99DE-47DA-B08A-6DD56FEBC7A4}" name="Cap_Input2_existing"/>
@@ -1397,7 +1400,7 @@
     <tableColumn id="21" xr3:uid="{EC2CC790-C17D-4744-A981-3984808E5B33}" name="vom_cost_Input2"/>
     <tableColumn id="24" xr3:uid="{41B338E4-2058-41E9-8000-97D77450FBC3}" name="vom_cost_Output1"/>
     <tableColumn id="25" xr3:uid="{DDAFCF0A-1EF1-4B7B-9742-01F9FA7A22E5}" name="vom_cost_Output2"/>
-    <tableColumn id="29" xr3:uid="{79DE3A19-CED6-47DE-AEF5-F6BB2D320F24}" name="connection_investment_tech_lifetime" dataDxfId="0"/>
+    <tableColumn id="29" xr3:uid="{79DE3A19-CED6-47DE-AEF5-F6BB2D320F24}" name="connection_investment_tech_lifetime" dataDxfId="1"/>
     <tableColumn id="30" xr3:uid="{09434E4A-7BF5-4547-9708-EA3F0F7ADC8E}" name="initial_connections_invested_available"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1408,7 +1411,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}" name="Table134" displayName="Table134" ref="A1:K5" totalsRowShown="0">
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A100,ISNUMBER(FIND("storage",Connections!A2:A100)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{8C29206C-8DC6-44DB-A8D1-3D5625C277AD}" name="Object_type"/>
@@ -1733,20 +1736,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1757,7 +1767,7 @@
         <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
@@ -1766,16 +1776,16 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J1" t="s">
         <v>64</v>
@@ -1813,33 +1823,33 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1887,7 +1897,7 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>42</v>
@@ -1898,13 +1908,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1927,10 +1937,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
@@ -1940,10 +1950,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
         <v>82</v>
@@ -1953,16 +1963,16 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H12">
         <v>50</v>
@@ -1974,35 +1984,22 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>88</v>
+      <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P14" xr:uid="{D92CB468-B7A9-4082-9B81-D3B4634F286E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P13" xr:uid="{D92CB468-B7A9-4082-9B81-D3B4634F286E}">
       <formula1>"h, D, W, M, Q, Y"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2028,12 +2025,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="7" max="8" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -2050,10 +2055,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>3</v>
@@ -2062,31 +2067,31 @@
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -2101,7 +2106,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="7"/>
@@ -2116,7 +2121,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>62</v>
@@ -2126,7 +2131,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -2141,7 +2146,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -2151,7 +2156,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -2183,7 +2188,7 @@
         <v>78</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -2240,7 +2245,7 @@
         <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>78</v>
@@ -2248,10 +2253,10 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -2271,10 +2276,10 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>78</v>
@@ -2289,7 +2294,7 @@
         <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -2318,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>75</v>
@@ -2345,13 +2350,13 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>75</v>
@@ -2362,13 +2367,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2391,10 +2396,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>78</v>
@@ -2403,21 +2408,19 @@
         <v>70</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>75</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>87</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="J12" s="3"/>
       <c r="K12" s="6">
         <v>42.75</v>
       </c>
@@ -2431,26 +2434,26 @@
       <c r="O12" s="6">
         <v>6.7340067340067344</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="8">
         <v>5.5096418732782366</v>
       </c>
       <c r="Q12" s="6"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>89</v>
+      <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -2459,40 +2462,11 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4">
-        <v>1.1883541295306002</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6">
-        <v>1</v>
-      </c>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2507,7 +2481,7 @@
           <x14:formula1>
             <xm:f>Drop_Down!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>B1:B14</xm:sqref>
+          <xm:sqref>B1:B13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2520,28 +2494,29 @@
   <dimension ref="A1:AA11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.85546875" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" customWidth="1"/>
-    <col min="22" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -2744,22 +2719,22 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G4" t="s">
         <v>32</v>
@@ -2776,7 +2751,7 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
         <v>74</v>
@@ -2808,7 +2783,7 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -2817,15 +2792,15 @@
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F6" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" t="s">
         <v>32</v>
       </c>
       <c r="H6">
@@ -2858,7 +2833,7 @@
       <c r="T6">
         <v>1</v>
       </c>
-      <c r="Z6" s="9" t="s">
+      <c r="Z6" t="s">
         <v>58</v>
       </c>
       <c r="AA6">
@@ -2867,18 +2842,18 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
       <c r="H7">
@@ -2896,7 +2871,7 @@
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="Z7" s="9" t="s">
+      <c r="Z7" t="s">
         <v>58</v>
       </c>
       <c r="AA7">
@@ -2905,7 +2880,7 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -2914,15 +2889,15 @@
         <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F8" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" t="s">
         <v>32</v>
       </c>
       <c r="H8">
@@ -2955,7 +2930,7 @@
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="Z8" s="9" t="s">
+      <c r="Z8" t="s">
         <v>58</v>
       </c>
       <c r="AA8">
@@ -2964,18 +2939,18 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" t="s">
         <v>32</v>
       </c>
       <c r="H9">
@@ -2993,7 +2968,7 @@
       <c r="T9">
         <v>1</v>
       </c>
-      <c r="Z9" s="9" t="s">
+      <c r="Z9" t="s">
         <v>58</v>
       </c>
       <c r="AA9">
@@ -3002,7 +2977,7 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
         <v>53</v>
@@ -3011,15 +2986,15 @@
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" t="s">
         <v>32</v>
       </c>
       <c r="H10">
@@ -3052,7 +3027,7 @@
       <c r="T10">
         <v>1</v>
       </c>
-      <c r="Z10" s="9" t="s">
+      <c r="Z10" t="s">
         <v>58</v>
       </c>
       <c r="AA10">
@@ -3061,18 +3036,18 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B11" t="s">
         <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" t="s">
         <v>32</v>
       </c>
       <c r="H11">
@@ -3090,7 +3065,7 @@
       <c r="T11">
         <v>1</v>
       </c>
-      <c r="Z11" s="9" t="s">
+      <c r="Z11" t="s">
         <v>58</v>
       </c>
       <c r="AA11">
@@ -3200,10 +3175,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3350,32 +3325,32 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/diesel/Model_Data_Base_diesel.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/diesel/Model_Data_Base_diesel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\diesel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\diesel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FFF786-3F88-4F30-AF42-3C5AA8EDFD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9575027-4C77-476E-BCBF-F78FA1123CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-10110" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" concurrentManualCount="6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="133">
   <si>
     <t>Unit</t>
   </si>
@@ -295,12 +295,6 @@
     <t>power_wholesale</t>
   </si>
   <si>
-    <t>pl_dh</t>
-  </si>
-  <si>
-    <t>dh</t>
-  </si>
-  <si>
     <t>water</t>
   </si>
   <si>
@@ -479,9 +473,6 @@
   </si>
   <si>
     <t>excess_heat</t>
-  </si>
-  <si>
-    <t>heat</t>
   </si>
 </sst>
 </file>
@@ -613,6 +604,12 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1298,12 +1295,6 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1337,8 +1328,8 @@
     <tableColumn id="12" xr3:uid="{F1A83AF0-CF23-4B00-9076-4E28DF8DAFD3}" name="fom_cost"/>
     <tableColumn id="21" xr3:uid="{400CD12D-8ADA-4557-B7CA-1464809EAFF0}" name="vom_cost"/>
     <tableColumn id="15" xr3:uid="{3F5A9F9C-E4A0-47A3-8DED-03601A5E69E7}" name="minimum_op_point"/>
-    <tableColumn id="38" xr3:uid="{957AF85B-8792-4643-A381-29FACAA69887}" name="resolution_output" dataDxfId="26"/>
-    <tableColumn id="39" xr3:uid="{BCE2350E-150B-4A7E-94BF-BB3BC7E31016}" name="demand" dataDxfId="25"/>
+    <tableColumn id="38" xr3:uid="{957AF85B-8792-4643-A381-29FACAA69887}" name="resolution_output" dataDxfId="4"/>
+    <tableColumn id="39" xr3:uid="{BCE2350E-150B-4A7E-94BF-BB3BC7E31016}" name="demand" dataDxfId="3"/>
     <tableColumn id="16" xr3:uid="{5F06ED78-6F41-4BEA-9209-36407E8BCFDC}" name="initial_units_on"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1346,34 +1337,34 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}" name="Table5" displayName="Table5" ref="A1:Q13" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}" name="Table5" displayName="Table5" ref="A1:Q13" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <autoFilter ref="A1:Q13" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{2BE3E317-773B-4E82-9035-69A43C6CB21B}" name="Unit" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{22613EE0-390D-4B04-9A9B-6D5554D1C8ED}" name="Object_type" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{54CD83B6-B63A-4ABD-99BD-9ED391BFB078}" name="Input1" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{F183F72C-A42E-4046-9CA2-B23C4DD3765C}" name="Input2" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{CA468CF3-FA3A-4DED-8C1A-ED8385FD2167}" name="Input3" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{6C9174ED-453E-45B1-B2C9-DC69B7CB535A}" name="Input4" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{513A63E4-7BE3-4AF5-AC5E-11EB4AF0D7AD}" name="Output1" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{4623E738-60A2-497B-BD61-91A608129A61}" name="Output2" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{5596B30B-5CDD-4E38-8C15-9C5F774E9B1F}" name="Output3" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{CD6FCAF1-2543-4CF8-99F5-E24DBA2DEDC0}" name="Output4" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{88F2DAC4-E2C3-4C34-B709-2523E8BE5B1F}" name="Relation_In1_In2" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{3C190E97-FD9A-4F36-8EBF-717B1ECA00B1}" name="Relation_In1_In3" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{043147D8-AE82-457E-8F19-EB4AE9D43B9E}" name="Relation_In1_In4" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{A190E492-7FDF-403D-B8AF-17448A48E47F}" name="Relation_In1_Out1" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{26E8D274-C985-4E20-8920-2BAC0A372552}" name="Relation_Out1_Out2" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{4E0BCAE8-11F8-4D98-AECC-86C8A3C2B5C1}" name="Relation_Out1_Out3" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{3C0369D5-4DD0-4B4B-9480-0C4665C0BC59}" name="Relation_Out1_Out4" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{2BE3E317-773B-4E82-9035-69A43C6CB21B}" name="Unit" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{22613EE0-390D-4B04-9A9B-6D5554D1C8ED}" name="Object_type" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{54CD83B6-B63A-4ABD-99BD-9ED391BFB078}" name="Input1" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{F183F72C-A42E-4046-9CA2-B23C4DD3765C}" name="Input2" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{CA468CF3-FA3A-4DED-8C1A-ED8385FD2167}" name="Input3" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{6C9174ED-453E-45B1-B2C9-DC69B7CB535A}" name="Input4" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{513A63E4-7BE3-4AF5-AC5E-11EB4AF0D7AD}" name="Output1" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{4623E738-60A2-497B-BD61-91A608129A61}" name="Output2" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{5596B30B-5CDD-4E38-8C15-9C5F774E9B1F}" name="Output3" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{CD6FCAF1-2543-4CF8-99F5-E24DBA2DEDC0}" name="Output4" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{88F2DAC4-E2C3-4C34-B709-2523E8BE5B1F}" name="Relation_In1_In2" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{3C190E97-FD9A-4F36-8EBF-717B1ECA00B1}" name="Relation_In1_In3" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{043147D8-AE82-457E-8F19-EB4AE9D43B9E}" name="Relation_In1_In4" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{A190E492-7FDF-403D-B8AF-17448A48E47F}" name="Relation_In1_Out1" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{26E8D274-C985-4E20-8920-2BAC0A372552}" name="Relation_Out1_Out2" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{4E0BCAE8-11F8-4D98-AECC-86C8A3C2B5C1}" name="Relation_Out1_Out3" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{3C0369D5-4DD0-4B4B-9480-0C4665C0BC59}" name="Relation_Out1_Out4" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA11" totalsRowShown="0">
-  <autoFilter ref="A1:AA11" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA10" totalsRowShown="0">
+  <autoFilter ref="A1:AA10" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{26B0CA71-1EA9-44CF-8E6D-31054ECA99A6}" name="Connection"/>
     <tableColumn id="26" xr3:uid="{E67F4435-EF76-417C-B715-53719E5FB41F}" name="Object_type"/>
@@ -1412,7 +1403,7 @@
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0">
-      <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A100,ISNUMBER(FIND("storage",Connections!A2:A100)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A99,ISNUMBER(FIND("storage",Connections!A2:A99)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{8C29206C-8DC6-44DB-A8D1-3D5625C277AD}" name="Object_type"/>
     <tableColumn id="4" xr3:uid="{AEAA1B51-84C1-491F-81D5-7757B30BDCCD}" name="value_before"/>
@@ -1737,29 +1728,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1767,7 +1758,7 @@
         <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
@@ -1776,16 +1767,16 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J1" t="s">
         <v>64</v>
@@ -1812,10 +1803,10 @@
         <v>41</v>
       </c>
       <c r="R1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1823,40 +1814,40 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -1876,9 +1867,9 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1889,15 +1880,15 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>42</v>
@@ -1906,22 +1897,22 @@
         <v>20.192799999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
@@ -1935,44 +1926,44 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H12">
         <v>50</v>
@@ -1983,12 +1974,12 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
@@ -2026,22 +2017,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2055,10 +2046,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>3</v>
@@ -2067,34 +2058,34 @@
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="P1" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>69</v>
       </c>
@@ -2106,7 +2097,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="7"/>
@@ -2119,9 +2110,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>62</v>
@@ -2131,7 +2122,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -2144,9 +2135,9 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -2156,7 +2147,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -2169,9 +2160,9 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>60</v>
@@ -2180,15 +2171,15 @@
         <v>70</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -2204,9 +2195,9 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>25</v>
@@ -2215,12 +2206,12 @@
         <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -2237,26 +2228,26 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -2274,27 +2265,27 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -2315,23 +2306,23 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -2348,38 +2339,38 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -2394,31 +2385,31 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="6">
@@ -2439,12 +2430,12 @@
       </c>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>70</v>
@@ -2453,7 +2444,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -2491,35 +2482,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -2602,7 +2593,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -2661,24 +2652,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
         <v>32</v>
@@ -2717,24 +2708,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G4" t="s">
         <v>32</v>
@@ -2743,18 +2734,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>123</v>
+      </c>
+      <c r="F5" t="s">
+        <v>72</v>
       </c>
       <c r="G5" t="s">
         <v>32</v>
@@ -2765,11 +2762,26 @@
       <c r="I5">
         <v>1000</v>
       </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
       <c r="L5">
         <v>1000</v>
       </c>
       <c r="M5">
         <v>1000</v>
+      </c>
+      <c r="N5">
+        <v>1000</v>
+      </c>
+      <c r="O5">
+        <v>1000</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -2781,24 +2793,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G6" t="s">
         <v>32</v>
@@ -2809,26 +2815,11 @@
       <c r="I6">
         <v>1000</v>
       </c>
-      <c r="J6">
-        <v>1000</v>
-      </c>
-      <c r="K6">
-        <v>1000</v>
-      </c>
       <c r="L6">
         <v>1000</v>
       </c>
       <c r="M6">
         <v>1000</v>
-      </c>
-      <c r="N6">
-        <v>1000</v>
-      </c>
-      <c r="O6">
-        <v>1000</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
       </c>
       <c r="T6">
         <v>1</v>
@@ -2840,18 +2831,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>124</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>124</v>
+      </c>
+      <c r="F7" t="s">
+        <v>72</v>
       </c>
       <c r="G7" t="s">
         <v>32</v>
@@ -2862,11 +2859,26 @@
       <c r="I7">
         <v>1000</v>
       </c>
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
       <c r="L7">
         <v>1000</v>
       </c>
       <c r="M7">
         <v>1000</v>
+      </c>
+      <c r="N7">
+        <v>1000</v>
+      </c>
+      <c r="O7">
+        <v>1000</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
       </c>
       <c r="T7">
         <v>1</v>
@@ -2878,24 +2890,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -2906,26 +2912,11 @@
       <c r="I8">
         <v>1000</v>
       </c>
-      <c r="J8">
-        <v>1000</v>
-      </c>
-      <c r="K8">
-        <v>1000</v>
-      </c>
       <c r="L8">
         <v>1000</v>
       </c>
       <c r="M8">
         <v>1000</v>
-      </c>
-      <c r="N8">
-        <v>1000</v>
-      </c>
-      <c r="O8">
-        <v>1000</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -2937,18 +2928,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>125</v>
+      </c>
+      <c r="F9" t="s">
+        <v>72</v>
       </c>
       <c r="G9" t="s">
         <v>32</v>
@@ -2959,11 +2956,26 @@
       <c r="I9">
         <v>1000</v>
       </c>
+      <c r="J9">
+        <v>1000</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
       <c r="L9">
         <v>1000</v>
       </c>
       <c r="M9">
         <v>1000</v>
+      </c>
+      <c r="N9">
+        <v>1000</v>
+      </c>
+      <c r="O9">
+        <v>1000</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
       </c>
       <c r="T9">
         <v>1</v>
@@ -2975,24 +2987,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
         <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
         <v>32</v>
@@ -3003,26 +3009,11 @@
       <c r="I10">
         <v>1000</v>
       </c>
-      <c r="J10">
-        <v>1000</v>
-      </c>
-      <c r="K10">
-        <v>1000</v>
-      </c>
       <c r="L10">
         <v>1000</v>
       </c>
       <c r="M10">
         <v>1000</v>
-      </c>
-      <c r="N10">
-        <v>1000</v>
-      </c>
-      <c r="O10">
-        <v>1000</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -3031,44 +3022,6 @@
         <v>58</v>
       </c>
       <c r="AA10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11">
-        <v>1000</v>
-      </c>
-      <c r="I11">
-        <v>1000</v>
-      </c>
-      <c r="L11">
-        <v>1000</v>
-      </c>
-      <c r="M11">
-        <v>1000</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA11">
         <v>1</v>
       </c>
     </row>
@@ -3086,7 +3039,7 @@
           <x14:formula1>
             <xm:f>Drop_Down!$A$2:$A$60</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B100</xm:sqref>
+          <xm:sqref>B2:B99</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3097,22 +3050,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -3147,9 +3100,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3173,12 +3126,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3228,129 +3181,129 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DC79B9-9C58-497E-9FD8-D3F2239E9BDC}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
